--- a/data/trans_orig/IP2004-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87053</t>
+          <t>87358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94394</t>
+          <t>94399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179235</t>
+          <t>179131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186066</t>
+          <t>186064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73906</t>
+          <t>74134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80700</t>
+          <t>80690</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77599</t>
+          <t>78193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154281</t>
+          <t>154793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161516</t>
+          <t>161702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92248</t>
+          <t>91700</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97158</t>
+          <t>97155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156382</t>
+          <t>156208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161163</t>
+          <t>161164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183575</t>
+          <t>183497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190351</t>
+          <t>190367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174092</t>
+          <t>174681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183123</t>
+          <t>183095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>360689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371775</t>
+          <t>371911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91699</t>
+          <t>91659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98209</t>
+          <t>98146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107740</t>
+          <t>108242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116494</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202300</t>
+          <t>202918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212904</t>
+          <t>213289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65443</t>
+          <t>65375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>70875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61093</t>
+          <t>61740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129553</t>
+          <t>129177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135959</t>
+          <t>135971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24067</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580062</t>
+          <t>579647</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>593003</t>
+          <t>593177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618778</t>
+          <t>617773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631185</t>
+          <t>631355</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1201820</t>
+          <t>1202452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1221109</t>
+          <t>1221926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76395</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82589</t>
+          <t>82593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79480</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158914</t>
+          <t>159195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165225</t>
+          <t>165224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81208</t>
+          <t>81318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86082</t>
+          <t>86087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>87844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178147</t>
+          <t>178153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75827</t>
+          <t>75130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80747</t>
+          <t>80745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77111</t>
+          <t>77016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155465</t>
+          <t>155790</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162236</t>
+          <t>162224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181344</t>
+          <t>181081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188288</t>
+          <t>188199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200923</t>
+          <t>200686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208038</t>
+          <t>208039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384796</t>
+          <t>384581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394793</t>
+          <t>394615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126759</t>
+          <t>127154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135238</t>
+          <t>135298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118593</t>
+          <t>118784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127438</t>
+          <t>127859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249003</t>
+          <t>248572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261035</t>
+          <t>260833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44974</t>
+          <t>45050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65603</t>
+          <t>65576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113070</t>
+          <t>112526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117957</t>
+          <t>117959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43835</t>
+          <t>42785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602847</t>
+          <t>602086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617103</t>
+          <t>617432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>643728</t>
+          <t>643839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>657199</t>
+          <t>657080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1252091</t>
+          <t>1253141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1270720</t>
+          <t>1271691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71773</t>
+          <t>72581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86570</t>
+          <t>86786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161341</t>
+          <t>161592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90351</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>195987</t>
+          <t>196432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124957</t>
+          <t>124369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193910</t>
+          <t>193583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203378</t>
+          <t>203454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193717</t>
+          <t>194542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201758</t>
+          <t>201783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392190</t>
+          <t>391303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404291</t>
+          <t>404048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122476</t>
+          <t>122281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129273</t>
+          <t>129276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124489</t>
+          <t>124632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132400</t>
+          <t>132437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250737</t>
+          <t>250237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260674</t>
+          <t>260543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>53545</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61553</t>
+          <t>60843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117025</t>
+          <t>117473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25490</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>37315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602574</t>
+          <t>602637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>616880</t>
+          <t>616676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>653007</t>
+          <t>651952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663839</t>
+          <t>663648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1259457</t>
+          <t>1260465</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1277616</t>
+          <t>1277287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99129</t>
+          <t>99253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127886</t>
+          <t>128845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134863</t>
+          <t>135022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230806</t>
+          <t>229993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237800</t>
+          <t>237811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88209</t>
+          <t>87890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181823</t>
+          <t>181214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>60114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>108429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>208220</t>
+          <t>208059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>213559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203255</t>
+          <t>203761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211023</t>
+          <t>211210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414832</t>
+          <t>414559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424147</t>
+          <t>423880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110651</t>
+          <t>110627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149057</t>
+          <t>149894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158122</t>
+          <t>158243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263470</t>
+          <t>263229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273534</t>
+          <t>273350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61961</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63100</t>
+          <t>62996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129925</t>
+          <t>129928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138141</t>
+          <t>138459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>34145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634431</t>
+          <t>633888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644170</t>
+          <t>644232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710663</t>
+          <t>710143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>724855</t>
+          <t>724808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1349375</t>
+          <t>1349023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1367398</t>
+          <t>1367017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
